--- a/Hoadon/HDRa/7/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/7/HDDienTuMayTinhTien.xlsx
@@ -302,225 +302,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>C25MLH</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>31/07/2025</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>3502551856</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>3502215269</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ DU LỊCH NGUYỄN HÀ</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Số 263 Lê Hồng Phong, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="13" t="n">
-        <v>570000.0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>570000.0</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn đã bị thay thế</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>C25MLH</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>31/07/2025</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>3502551856</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>3500835690</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="13" t="n">
-        <v>3.290389E7</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>1645195.0</v>
-      </c>
-      <c r="N8" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="13" t="n">
-        <v>3.4549085E7</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>C25MLH</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>31/07/2025</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>3502551856</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>3502468615</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THỰC PHẨM LONG HƯNG PHÁT</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Số 207/8 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành phố Hồ chí Minh Việt Nam</t>
-        </is>
-      </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="13" t="n">
-        <v>8.770758E7</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>4385379.0</v>
-      </c>
-      <c r="N9" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="13" t="n">
-        <v>9.2092959E7</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
